--- a/artfynd/A 14696-2026 artfynd.xlsx
+++ b/artfynd/A 14696-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101682450</v>
+        <v>129224244</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelåsstugan, Gstr</t>
+          <t>Kungsberg, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578134.5779361883</v>
+        <v>577992</v>
       </c>
       <c r="R2" t="n">
-        <v>6731409.592451159</v>
+        <v>6731457</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,62 +769,61 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Söderlund</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Söderlund</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104158398</v>
+        <v>129224211</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kungsberg, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578135.5369893925</v>
+        <v>578084</v>
       </c>
       <c r="R3" t="n">
-        <v>6731410.592632815</v>
+        <v>6731525</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,27 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-31</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,16 +890,11 @@
         <v>118950864</v>
       </c>
       <c r="B4" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1030,11 +997,11 @@
         <v>129224212</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1130,6 +1097,852 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>101682450</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gammelåsstugan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>578135</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6731409</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-05-31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-05-31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erik Söderlund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Söderlund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104158398</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kungsberg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>578136</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6731410</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-05-31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-05-31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129224239</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kungsberg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>578008</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6731472</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129224240</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kungsberg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>578014</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6731468</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129224246</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kungsberg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>577992</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6731457</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129224249</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kungsberg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>578000</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6731484</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129224250</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kungsberg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>578003</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6731478</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129224251</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kungsberg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>578000</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6731472</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14696-2026 artfynd.xlsx
+++ b/artfynd/A 14696-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224244</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224211</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118950864</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224212</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101682450</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104158398</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,6 +1448,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224239</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1519,6 +1559,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224240</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224246</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1731,6 +1781,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224249</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1837,6 +1892,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224250</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1943,8 +2003,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224251</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>